--- a/duoki_editor/resources/data/blank/服装店-自由画画-5-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-自由画画-5-blank.xlsx
@@ -121,7 +121,7 @@
     <t>快把橙色边框的短裤放在玩偶身上吧！</t>
   </si>
   <si>
-    <t>时间快来不及了！把橙色边框的短裤放在玩偶身上上吧！</t>
+    <t>时间快来不及了！把橙色边框的短裤放在玩偶身上吧！</t>
   </si>
   <si>
     <t>200405|200435</t>
